--- a/outputs/Block5B_Senate_Validation_Summary.xlsx
+++ b/outputs/Block5B_Senate_Validation_Summary.xlsx
@@ -533,7 +533,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5.030461973215973</v>
+        <v>5.335678432032632</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -541,7 +541,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>5.116327771031301</v>
+        <v>5.392670902908676</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>-0.4600969645272963</v>
+        <v>-0.1837538326499217</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -557,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -565,7 +565,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -573,7 +573,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -589,7 +589,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>30.31658358414894</v>
+        <v>33.17720407829815</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -597,7 +597,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>0.05605193420956077</v>
+        <v>0.04962109397452368</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -605,7 +605,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>0.05055120001657485</v>
+        <v>0.05044507070408787</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -613,7 +613,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>0.1778338438381567</v>
+        <v>0.1599892752069019</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -621,7 +621,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.1572465454955758</v>
+        <v>0.1571121845378949</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -629,7 +629,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.8823529411764706</v>
+        <v>0.7941176470588235</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -637,7 +637,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.9411764705882353</v>
+        <v>0.8823529411764706</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -645,7 +645,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.111210061863166</v>
+        <v>0.8436468628413508</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -661,7 +661,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>1.111210061863166</v>
+        <v>0.8436468628413508</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -725,7 +725,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>1.05088293363535</v>
+        <v>0.756804455446531</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -733,7 +733,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
